--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R210-ActeSpecifique.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5599" uniqueCount="3838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5600" uniqueCount="3839">
   <si>
     <t>Property</t>
   </si>
@@ -4951,13 +4951,13 @@
     <t>0764</t>
   </si>
   <si>
-    <t>Soins de stomie d'élimination digestive</t>
+    <t>Suivi et surveillance de stomie d'élimination digestive</t>
   </si>
   <si>
     <t>0765</t>
   </si>
   <si>
-    <t>Soins de stomie d'élimination urinaire</t>
+    <t>Suivi et surveillance de stomie d'élimination urinaire</t>
   </si>
   <si>
     <t>0766</t>
@@ -11479,7 +11479,7 @@
     <t>1720</t>
   </si>
   <si>
-    <t>Programme de psychoéducation psy pour les familles et aidants (ProFamille, BREF...)</t>
+    <t>Programme de psychoéducation psychiatrique pour les familles et aidants (ProFamille, BREF...)</t>
   </si>
   <si>
     <t>Programme structuré d'intervention thérapeutique destiné aux familles et aidants de personnes souffrant d'un trouble psychiatrique, visant à les informer sur la maladie, renforcer leurs capacités à accompagner le patient et prévenir leur propre épuisement.</t>
@@ -11525,6 +11525,9 @@
   </si>
   <si>
     <t>Tomothérapie</t>
+  </si>
+  <si>
+    <t>La tomothérapie est une technique avancée de radiothérapie qui combine un scanner et un accélérateur de particules afin de délivrer les rayonnements avec une très grande précision autour de la tumeur tout en limitant l'irradiation des tissus sains.</t>
   </si>
   <si>
     <t>Centre expert Epileptologie</t>
@@ -33376,7 +33379,9 @@
       <c r="C1728" t="s" s="2">
         <v>3836</v>
       </c>
-      <c r="D1728" s="2"/>
+      <c r="D1728" t="s" s="2">
+        <v>3837</v>
+      </c>
     </row>
     <row r="1729">
       <c r="A1729" t="s" s="2">
@@ -33386,7 +33391,7 @@
         <v>34</v>
       </c>
       <c r="C1729" t="s" s="2">
-        <v>3837</v>
+        <v>3838</v>
       </c>
       <c r="D1729" s="2"/>
     </row>
